--- a/Change Management Tracker (1).xlsx
+++ b/Change Management Tracker (1).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="147">
   <si>
     <t>ECN/PCN No</t>
   </si>
@@ -107,7 +107,10 @@
     <t>ECN Status</t>
   </si>
   <si>
-    <t>Remarks</t>
+    <t>Open Points</t>
+  </si>
+  <si>
+    <t>Open Points-Team</t>
   </si>
   <si>
     <t>ECN/2026/001</t>
@@ -167,6 +170,9 @@
     <t>Open</t>
   </si>
   <si>
+    <t>R&amp;D</t>
+  </si>
+  <si>
     <t>ECN/2026/002</t>
   </si>
   <si>
@@ -188,7 +194,10 @@
     <t>ECR-1.45 g/cc</t>
   </si>
   <si>
-    <t>Risks associated with low peel strength, JR OD rejections and pressure NGs in can insertion discussed along with the action plan addressing these issues.</t>
+    <t>Need to update the trial results. High OD and pressure NG even after revising the spec of avg OD to 44.6 mm</t>
+  </si>
+  <si>
+    <t>R&amp;D &amp; ME</t>
   </si>
   <si>
     <t>ECN/2026/003</t>
@@ -197,6 +206,9 @@
     <t>Trim Recycling - Cathode + Anode</t>
   </si>
   <si>
+    <t>ME/R&amp;D/QC</t>
+  </si>
+  <si>
     <t>New process Implementation</t>
   </si>
   <si>
@@ -212,12 +224,21 @@
     <t>Anode + Cathode Area</t>
   </si>
   <si>
-    <t>ECR-Trim Loss</t>
+    <t>ECR-Cathode Bottom Trim Loss</t>
   </si>
   <si>
     <t>Contamination</t>
   </si>
   <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Approved for BESS Applications</t>
+  </si>
+  <si>
+    <t>ME</t>
+  </si>
+  <si>
     <t>ECN/2026/004</t>
   </si>
   <si>
@@ -323,9 +344,6 @@
     <t>Delayed</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>ECR-Sign off Ongoing</t>
   </si>
   <si>
@@ -359,6 +377,9 @@
     <t>ECR-Sign off Done</t>
   </si>
   <si>
+    <t>ECR Signoff Done, Specification Sheet signoff ongoing</t>
+  </si>
+  <si>
     <t>ECN/2026/011</t>
   </si>
   <si>
@@ -387,9 +408,6 @@
   </si>
   <si>
     <t>JR OD upper spec revision to 44.55 mm from 44.4 mm</t>
-  </si>
-  <si>
-    <t>ME/R&amp;D/QC</t>
   </si>
   <si>
     <t>Specification Change</t>
@@ -446,7 +464,7 @@
     <numFmt numFmtId="165" formatCode="d-mmmm-yy"/>
     <numFmt numFmtId="166" formatCode="d mmm yyyy"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -463,6 +481,14 @@
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF0000FF"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF0000FF"/>
     </font>
   </fonts>
   <fills count="3">
@@ -499,7 +525,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -512,11 +538,17 @@
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
@@ -747,6 +779,7 @@
     <col customWidth="1" min="2" max="2" width="51.13"/>
     <col customWidth="1" min="3" max="4" width="50.88"/>
     <col customWidth="1" min="5" max="6" width="42.88"/>
+    <col customWidth="1" min="10" max="10" width="17.63"/>
     <col customWidth="1" min="21" max="21" width="23.75"/>
     <col customWidth="1" min="26" max="26" width="11.88"/>
   </cols>
@@ -854,1232 +887,1267 @@
       <c r="AH1" s="1" t="s">
         <v>31</v>
       </c>
+      <c r="AI1" s="1" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="J2" s="2" t="s">
         <v>41</v>
       </c>
+      <c r="J2" s="4" t="s">
+        <v>42</v>
+      </c>
       <c r="K2" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L2" s="4">
+        <v>43</v>
+      </c>
+      <c r="L2" s="5">
         <v>46078.0</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="X2" s="5">
+        <v>48</v>
+      </c>
+      <c r="X2" s="6">
         <v>46173.0</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Z2" s="2">
         <v>22.0</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AG2" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AH2" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="AI2" s="3" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="F3" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>59</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L3" s="4">
+        <v>43</v>
+      </c>
+      <c r="L3" s="5">
         <v>46078.0</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="V3" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="W3" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="X3" s="5">
+        <v>48</v>
+      </c>
+      <c r="X3" s="6">
         <v>46173.0</v>
       </c>
       <c r="Y3" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Z3" s="2">
         <v>22.0</v>
       </c>
       <c r="AA3" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AB3" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AC3" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AD3" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AE3" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AF3" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AG3" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AH3" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
+      </c>
+      <c r="AI3" s="3" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>70</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L4" s="4">
+        <v>43</v>
+      </c>
+      <c r="L4" s="5">
         <v>46118.0</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="X4" s="5">
+        <v>48</v>
+      </c>
+      <c r="X4" s="6">
         <v>46173.0</v>
       </c>
       <c r="Y4" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Z4" s="2">
         <v>22.0</v>
       </c>
       <c r="AA4" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AB4" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AC4" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AD4" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AE4" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AF4" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AG4" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AH4" s="3" t="s">
-        <v>44</v>
+        <v>73</v>
+      </c>
+      <c r="AI4" s="3" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="J5" s="6"/>
+        <v>82</v>
+      </c>
+      <c r="J5" s="8"/>
       <c r="K5" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="V5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="X5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Y5" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Z5" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AA5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AB5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AC5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AD5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AE5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AF5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AG5" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AH5" s="3" t="s">
-        <v>46</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="AI5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="D6" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E6" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="F6" s="3" t="s">
-        <v>72</v>
-      </c>
       <c r="G6" s="3" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="J6" s="6"/>
+        <v>82</v>
+      </c>
+      <c r="J6" s="8"/>
       <c r="K6" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U6" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="V6" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Y6" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Z6" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AA6" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AB6" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AC6" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AD6" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AE6" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AF6" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AG6" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AH6" s="3" t="s">
-        <v>46</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="AI6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E7" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="J7" s="8"/>
+      <c r="K7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P7" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="J7" s="6"/>
-      <c r="K7" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="Q7" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U7" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="V7" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="X7" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Y7" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Z7" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AA7" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AB7" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AC7" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AD7" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AE7" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AF7" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AG7" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AH7" s="3" t="s">
-        <v>46</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="AI7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E8" s="3" t="s">
+      <c r="F8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>72</v>
-      </c>
       <c r="G8" s="3" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="J8" s="6"/>
+        <v>96</v>
+      </c>
+      <c r="J8" s="8"/>
       <c r="K8" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="V8" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="X8" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Y8" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Z8" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AA8" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AB8" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AC8" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AD8" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AE8" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AF8" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AG8" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AH8" s="3" t="s">
-        <v>46</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="AI8" s="3"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="G9" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>98</v>
+      <c r="J9" s="4" t="s">
+        <v>105</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L9" s="4">
+        <v>43</v>
+      </c>
+      <c r="L9" s="5">
         <v>46095.0</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="U9" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="V9" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="X9" s="4">
+        <v>48</v>
+      </c>
+      <c r="X9" s="5">
         <v>46112.0</v>
       </c>
       <c r="Y9" s="2" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="Z9" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AA9" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AB9" s="2" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="AC9" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AD9" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AE9" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AF9" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AG9" s="3" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="AH9" s="3" t="s">
-        <v>46</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="AI9" s="3"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L10" s="5">
+        <v>46116.0</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="N10" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="D10" s="2" t="s">
+      <c r="O10" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L10" s="4">
-        <v>46116.0</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>100</v>
-      </c>
       <c r="P10" s="2" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="U10" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="V10" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="X10" s="4">
+        <v>48</v>
+      </c>
+      <c r="X10" s="5">
         <v>46112.0</v>
       </c>
       <c r="Y10" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Z10" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AA10" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AB10" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AC10" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AD10" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AE10" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AF10" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AG10" s="3" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="AH10" s="3" t="s">
-        <v>46</v>
+        <v>121</v>
+      </c>
+      <c r="AI10" s="3" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="G11" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L11" s="5">
+        <v>46128.0</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="P11" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L11" s="4">
-        <v>46128.0</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>113</v>
-      </c>
       <c r="Q11" s="2" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="U11" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="V11" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="X11" s="4">
+        <v>48</v>
+      </c>
+      <c r="X11" s="5">
         <v>46142.0</v>
       </c>
       <c r="Y11" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Z11" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AA11" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AB11" s="2" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="AC11" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AD11" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AE11" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AF11" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AG11" s="3" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="AH11" s="3" t="s">
-        <v>46</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="AI11" s="3"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>125</v>
+        <v>64</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>131</v>
+        <v>136</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>137</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L12" s="5">
+        <v>43</v>
+      </c>
+      <c r="L12" s="6">
         <v>46146.0</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>103</v>
+        <v>72</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="U12" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="V12" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="X12" s="5">
+        <v>48</v>
+      </c>
+      <c r="X12" s="6">
         <v>46152.0</v>
       </c>
       <c r="Y12" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Z12" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AA12" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AB12" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AC12" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AD12" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AE12" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AF12" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AG12" s="3" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="AH12" s="3" t="s">
-        <v>46</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="AI12" s="3"/>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>70</v>
+      <c r="A13" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>77</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="E13" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="E13" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="F13" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="F13" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>135</v>
+      <c r="G13" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>141</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="L13" s="8">
+        <v>142</v>
+      </c>
+      <c r="K13" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="L13" s="10">
         <v>46080.0</v>
       </c>
-      <c r="M13" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="N13" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="O13" s="7" t="s">
-        <v>100</v>
+      <c r="M13" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="N13" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="O13" s="9" t="s">
+        <v>107</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q13" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="R13" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="S13" s="8">
+        <v>119</v>
+      </c>
+      <c r="Q13" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="R13" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="S13" s="10">
         <v>46091.0</v>
       </c>
-      <c r="T13" s="7"/>
-      <c r="U13" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="V13" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="W13" s="7"/>
-      <c r="X13" s="7"/>
-      <c r="Y13" s="7"/>
-      <c r="Z13" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="AA13" s="7"/>
-      <c r="AB13" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="AC13" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="AD13" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="AE13" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="AF13" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="AG13" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="AH13" s="7"/>
+      <c r="T13" s="9"/>
+      <c r="U13" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="V13" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="W13" s="9"/>
+      <c r="X13" s="9"/>
+      <c r="Y13" s="9"/>
+      <c r="Z13" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="AA13" s="9"/>
+      <c r="AB13" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="AC13" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD13" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="AE13" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="AF13" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="AG13" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="AH13" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="AI13" s="9"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <hyperlinks>
+    <hyperlink r:id="rId1" ref="J2"/>
+    <hyperlink r:id="rId2" ref="J3"/>
+    <hyperlink r:id="rId3" location="gid=208841060" ref="J4"/>
+    <hyperlink r:id="rId4" location="gid=1007600012" ref="J9"/>
+    <hyperlink r:id="rId5" location="gid=1342738934" ref="J10"/>
+    <hyperlink r:id="rId6" location="gid=1007600012" ref="J11"/>
+    <hyperlink r:id="rId7" location="gid=1007600012" ref="J12"/>
+    <hyperlink r:id="rId8" location="gid=1007600012" ref="J13"/>
+  </hyperlinks>
+  <drawing r:id="rId9"/>
 </worksheet>
 </file>
--- a/Change Management Tracker (1).xlsx
+++ b/Change Management Tracker (1).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="147">
   <si>
     <t>ECN/PCN No</t>
   </si>
@@ -1313,7 +1313,9 @@
       <c r="AH5" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AI5" s="3"/>
+      <c r="AI5" s="3" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
@@ -1416,7 +1418,9 @@
       <c r="AH6" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AI6" s="3"/>
+      <c r="AI6" s="3" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
@@ -1515,7 +1519,9 @@
       <c r="AH7" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AI7" s="3"/>
+      <c r="AI7" s="3" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
@@ -1618,7 +1624,9 @@
       <c r="AH8" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AI8" s="3"/>
+      <c r="AI8" s="3" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
@@ -1723,7 +1731,9 @@
       <c r="AH9" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AI9" s="3"/>
+      <c r="AI9" s="3" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
@@ -1829,7 +1839,7 @@
         <v>121</v>
       </c>
       <c r="AI10" s="3" t="s">
-        <v>74</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11">
@@ -1935,7 +1945,9 @@
       <c r="AH11" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AI11" s="3"/>
+      <c r="AI11" s="3" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
@@ -2040,7 +2052,9 @@
       <c r="AH12" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AI12" s="3"/>
+      <c r="AI12" s="3" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="s">
@@ -2135,7 +2149,9 @@
       <c r="AH13" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AI13" s="9"/>
+      <c r="AI13" s="3" t="s">
+        <v>47</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>

--- a/Change Management Tracker (1).xlsx
+++ b/Change Management Tracker (1).xlsx
@@ -266,6 +266,9 @@
     <t>Upcoming</t>
   </si>
   <si>
+    <t>None</t>
+  </si>
+  <si>
     <t>ECN/2026/005</t>
   </si>
   <si>
@@ -314,9 +317,6 @@
     <t>Design</t>
   </si>
   <si>
-    <t>Balavinayagam Ramalingam</t>
-  </si>
-  <si>
     <t>QR Code Change</t>
   </si>
   <si>
@@ -353,9 +353,6 @@
     <t>Anode and Cathode Slitted Foils</t>
   </si>
   <si>
-    <t>None</t>
-  </si>
-  <si>
     <t>Incoming slitted foil-308 mm width in anode and 304 mm in cathode</t>
   </si>
   <si>
@@ -408,6 +405,9 @@
   </si>
   <si>
     <t>JR OD upper spec revision to 44.55 mm from 44.4 mm</t>
+  </si>
+  <si>
+    <t>ME/R&amp;D</t>
   </si>
   <si>
     <t>Specification Change</t>
@@ -1314,15 +1314,15 @@
         <v>47</v>
       </c>
       <c r="AI5" s="3" t="s">
-        <v>47</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>77</v>
@@ -1331,7 +1331,7 @@
         <v>36</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>79</v>
@@ -1340,7 +1340,7 @@
         <v>80</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>82</v>
@@ -1419,15 +1419,15 @@
         <v>47</v>
       </c>
       <c r="AI6" s="3" t="s">
-        <v>47</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>77</v>
@@ -1436,15 +1436,15 @@
         <v>36</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F7" s="9"/>
       <c r="G7" s="9"/>
       <c r="H7" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J7" s="8"/>
       <c r="K7" s="2" t="s">
@@ -1520,15 +1520,15 @@
         <v>47</v>
       </c>
       <c r="AI7" s="3" t="s">
-        <v>47</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>77</v>
@@ -1537,7 +1537,7 @@
         <v>36</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>79</v>
@@ -1546,10 +1546,10 @@
         <v>80</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J8" s="8"/>
       <c r="K8" s="2" t="s">
@@ -1625,21 +1625,21 @@
         <v>47</v>
       </c>
       <c r="AI8" s="3" t="s">
-        <v>47</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>101</v>
@@ -1654,7 +1654,7 @@
         <v>104</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>105</v>
@@ -1732,7 +1732,7 @@
         <v>47</v>
       </c>
       <c r="AI9" s="3" t="s">
-        <v>47</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10">
@@ -1743,28 +1743,28 @@
         <v>112</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D10" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="F10" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="G10" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="H10" s="3" t="s">
         <v>116</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>117</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>82</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>43</v>
@@ -1782,7 +1782,7 @@
         <v>107</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q10" s="2" t="s">
         <v>50</v>
@@ -1833,45 +1833,45 @@
         <v>47</v>
       </c>
       <c r="AG10" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="AH10" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="AH10" s="3" t="s">
-        <v>121</v>
-      </c>
       <c r="AI10" s="3" t="s">
-        <v>47</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="E11" s="3" t="s">
+      <c r="F11" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="G11" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="H11" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="H11" s="3" t="s">
+      <c r="I11" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="J11" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>129</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>43</v>
@@ -1889,7 +1889,7 @@
         <v>107</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q11" s="2" t="s">
         <v>72</v>
@@ -1946,21 +1946,21 @@
         <v>47</v>
       </c>
       <c r="AI11" s="3" t="s">
-        <v>47</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="C12" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>131</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>132</v>
@@ -1996,7 +1996,7 @@
         <v>107</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q12" s="2" t="s">
         <v>72</v>
@@ -2053,7 +2053,7 @@
         <v>47</v>
       </c>
       <c r="AI12" s="3" t="s">
-        <v>47</v>
+        <v>84</v>
       </c>
     </row>
     <row r="13">
@@ -2067,10 +2067,10 @@
         <v>77</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>79</v>
@@ -2103,7 +2103,7 @@
         <v>107</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q13" s="9" t="s">
         <v>143</v>
@@ -2150,7 +2150,7 @@
         <v>47</v>
       </c>
       <c r="AI13" s="3" t="s">
-        <v>47</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/Change Management Tracker (1).xlsx
+++ b/Change Management Tracker (1).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="157">
   <si>
     <t>ECN/PCN No</t>
   </si>
@@ -122,6 +122,9 @@
     <t>Process</t>
   </si>
   <si>
+    <t>None</t>
+  </si>
+  <si>
     <t>Recipe Change</t>
   </si>
   <si>
@@ -176,6 +179,9 @@
     <t>1.45 g/cc Anode Density electrode</t>
   </si>
   <si>
+    <t>All</t>
+  </si>
+  <si>
     <t>Anode Electrode Density-1.58 g/cc</t>
   </si>
   <si>
@@ -203,6 +209,9 @@
     <t>Trim Recycling - Cathode Bottom Trim</t>
   </si>
   <si>
+    <t>Bala/Rajesh</t>
+  </si>
+  <si>
     <t>New process Implementation</t>
   </si>
   <si>
@@ -254,9 +263,6 @@
     <t>Vendor Trials Done, equipment to be decided based on the results</t>
   </si>
   <si>
-    <t>None</t>
-  </si>
-  <si>
     <t>ECN/2026/006</t>
   </si>
   <si>
@@ -314,6 +320,9 @@
     <t>Assembly - A</t>
   </si>
   <si>
+    <t>No open points</t>
+  </si>
+  <si>
     <t>ECN/2026/010</t>
   </si>
   <si>
@@ -335,6 +344,9 @@
     <t>Design</t>
   </si>
   <si>
+    <t>Balavinayagam R</t>
+  </si>
+  <si>
     <t>QR Code Change</t>
   </si>
   <si>
@@ -371,6 +383,9 @@
     <t>Anode and Cathode Slitted Foils</t>
   </si>
   <si>
+    <t>Approval Done</t>
+  </si>
+  <si>
     <t>Incoming slitted foil-308 mm width in anode and 304 mm in cathode</t>
   </si>
   <si>
@@ -444,6 +459,9 @@
   </si>
   <si>
     <t>Semi Automated UV Curing</t>
+  </si>
+  <si>
+    <t>Balavinayagam</t>
   </si>
   <si>
     <t>To improve the throughput of the UV curing process</t>
@@ -558,11 +576,11 @@
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
+    </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="166" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -898,1557 +916,1585 @@
       <c r="C2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="E2" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L2" s="4">
         <v>46078.0</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="X2" s="5">
         <v>46173.0</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Z2" s="2">
         <v>19.0</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AB2" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AC2" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AD2" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AE2" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AF2" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AG2" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AH2" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AI2" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="E3" s="2" t="s">
         <v>35</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L3" s="4">
         <v>46078.0</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="V3" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="W3" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="X3" s="5">
         <v>46173.0</v>
       </c>
       <c r="Y3" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Z3" s="2">
         <v>19.0</v>
       </c>
       <c r="AA3" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AB3" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AC3" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AD3" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AE3" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AF3" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AG3" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AH3" s="2" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="AI3" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" s="2" t="s">
+        <v>65</v>
+      </c>
       <c r="E4" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L4" s="5">
         <v>46153.0</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="X4" s="5">
         <v>46173.0</v>
       </c>
       <c r="Y4" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Z4" s="2">
         <v>19.0</v>
       </c>
       <c r="AA4" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AB4" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AC4" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AD4" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AE4" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AF4" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AG4" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AH4" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="AI4" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="2"/>
+      <c r="D5" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="E5" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L5" s="4">
         <v>46118.0</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="V5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="X5" s="5">
         <v>46173.0</v>
       </c>
       <c r="Y5" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Z5" s="2" t="b">
         <v>0</v>
       </c>
       <c r="AA5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AB5" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AC5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AD5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AE5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AF5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AG5" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AH5" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="AI5" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="2"/>
+      <c r="D6" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="E6" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L6" s="4">
         <v>46118.0</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U6" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="V6" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="X6" s="5">
         <v>46173.0</v>
       </c>
       <c r="Y6" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Z6" s="2" t="b">
         <v>0</v>
       </c>
       <c r="AA6" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AB6" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AC6" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AD6" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AE6" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AF6" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AG6" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AH6" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AI6" s="2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="2"/>
+      <c r="D7" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="E7" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L7" s="4">
         <v>46118.0</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U7" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="V7" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="X7" s="5">
         <v>46173.0</v>
       </c>
       <c r="Y7" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Z7" s="2" t="b">
         <v>0</v>
       </c>
       <c r="AA7" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AB7" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AC7" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AD7" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AE7" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AF7" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AG7" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AH7" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="AI7" s="2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D8" s="2"/>
+        <v>87</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="E8" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="V8" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="X8" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Y8" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Z8" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="AA8" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AB8" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AC8" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AD8" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AE8" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AF8" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AG8" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AH8" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI8" s="2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>90</v>
-      </c>
       <c r="J9" s="6" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U9" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="V9" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="X9" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Y9" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Z9" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="AA9" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AB9" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AC9" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AD9" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AE9" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AF9" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AG9" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AH9" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI9" s="2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D10" s="2"/>
+        <v>87</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="E10" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
       <c r="H10" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U10" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="V10" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Y10" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Z10" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="AA10" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AB10" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AC10" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AD10" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AE10" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AF10" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AG10" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AH10" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI10" s="2" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D11" s="2"/>
+        <v>87</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="E11" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H11" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="T11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="U11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="V11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="W11" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="X11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y11" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z11" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="AA11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AC11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AD11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AE11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AF11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AG11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AH11" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AI11" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="R11" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="S11" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="T11" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="U11" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="V11" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="W11" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="X11" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y11" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="Z11" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="AA11" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB11" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="AC11" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="AD11" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="AE11" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="AF11" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="AG11" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="AH11" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="AI11" s="2" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>103</v>
-      </c>
       <c r="J12" s="3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L12" s="4">
         <v>46095.0</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="U12" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="V12" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="X12" s="4">
         <v>46112.0</v>
       </c>
       <c r="Y12" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="Z12" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="AA12" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AB12" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AC12" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AD12" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AE12" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AF12" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AG12" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AH12" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI12" s="2" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D13" s="2"/>
+        <v>109</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>123</v>
+      </c>
       <c r="E13" s="2" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L13" s="4">
         <v>46116.0</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="U13" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="V13" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="W13" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="X13" s="4">
         <v>46112.0</v>
       </c>
       <c r="Y13" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Z13" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="AA13" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AB13" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AC13" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AD13" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AE13" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AF13" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AG13" s="2" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="AH13" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI13" s="2" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D14" s="2"/>
+        <v>109</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>110</v>
+      </c>
       <c r="E14" s="2" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L14" s="4">
         <v>46128.0</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="U14" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="V14" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="W14" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="X14" s="4">
         <v>46142.0</v>
       </c>
       <c r="Y14" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Z14" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="AA14" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AB14" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="AC14" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AD14" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AE14" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AF14" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AG14" s="2" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="AH14" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI14" s="2" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D15" s="2"/>
+        <v>109</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>65</v>
+      </c>
       <c r="E15" s="2" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L15" s="5">
         <v>46146.0</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="U15" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="V15" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="W15" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="X15" s="5">
         <v>46152.0</v>
       </c>
       <c r="Y15" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="Z15" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="AA15" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AB15" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AC15" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AD15" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AE15" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AF15" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AG15" s="2" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="AH15" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI15" s="2" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>71</v>
+        <v>87</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>149</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="L16" s="9">
+        <v>43</v>
+      </c>
+      <c r="L16" s="8">
         <v>46080.0</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N16" s="7" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="O16" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="P16" s="8" t="s">
-        <v>114</v>
+        <v>117</v>
+      </c>
+      <c r="P16" s="9" t="s">
+        <v>118</v>
       </c>
       <c r="Q16" s="7" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="R16" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="S16" s="9">
+        <v>154</v>
+      </c>
+      <c r="S16" s="8">
         <v>46091.0</v>
       </c>
       <c r="T16" s="7"/>
       <c r="U16" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="V16" s="7" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="W16" s="7"/>
       <c r="X16" s="7"/>
       <c r="Y16" s="7"/>
       <c r="Z16" s="7" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AA16" s="7"/>
       <c r="AB16" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AC16" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AD16" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AE16" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AF16" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AG16" s="7" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="AH16" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI16" s="2" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/Change Management Tracker (1).xlsx
+++ b/Change Management Tracker (1).xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="156">
   <si>
     <t>ECN/PCN No</t>
   </si>
@@ -344,7 +344,7 @@
     <t>Design</t>
   </si>
   <si>
-    <t>Balavinayagam R</t>
+    <t>Bala</t>
   </si>
   <si>
     <t>QR Code Change</t>
@@ -459,9 +459,6 @@
   </si>
   <si>
     <t>Semi Automated UV Curing</t>
-  </si>
-  <si>
-    <t>Balavinayagam</t>
   </si>
   <si>
     <t>To improve the throughput of the UV curing process</t>
@@ -2411,7 +2408,7 @@
         <v>87</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>149</v>
+        <v>110</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>95</v>
@@ -2423,13 +2420,13 @@
         <v>89</v>
       </c>
       <c r="H16" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="I16" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="I16" s="7" t="s">
+      <c r="J16" s="3" t="s">
         <v>151</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>152</v>
       </c>
       <c r="K16" s="7" t="s">
         <v>43</v>
@@ -2450,10 +2447,10 @@
         <v>118</v>
       </c>
       <c r="Q16" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="R16" s="7" t="s">
         <v>153</v>
-      </c>
-      <c r="R16" s="7" t="s">
-        <v>154</v>
       </c>
       <c r="S16" s="8">
         <v>46091.0</v>
@@ -2463,7 +2460,7 @@
         <v>50</v>
       </c>
       <c r="V16" s="7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="W16" s="7"/>
       <c r="X16" s="7"/>
@@ -2488,7 +2485,7 @@
         <v>47</v>
       </c>
       <c r="AG16" s="7" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AH16" s="2" t="s">
         <v>47</v>
